--- a/03_Quiz/Q01_K04/vocab.xlsx
+++ b/03_Quiz/Q01_K04/vocab.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/iw/Documents/NTU/1132/1132_German_IV/03_Quiz/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/iw/Documents/NTU/1132/1132_German_IV/03_Quiz/Q01_K04/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{EC87F20D-ECE3-FB43-868C-B3E7FCD09902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE95A97A-CBE2-B54F-9A8B-AD1D91E33FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="320" yWindow="680" windowWidth="24940" windowHeight="15300" xr2:uid="{8ADE7F18-CB55-9243-B556-61F2463E6518}"/>
+    <workbookView xWindow="12880" yWindow="840" windowWidth="12560" windowHeight="15640" xr2:uid="{8ADE7F18-CB55-9243-B556-61F2463E6518}"/>
   </bookViews>
   <sheets>
     <sheet name="不認識 (2)" sheetId="4" r:id="rId1"/>
@@ -21,10 +21,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">工作表1!$A$1:$B$464</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">不認識!$A$1:$B$358</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'不認識 (2)'!$A$1:$B$291</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'不認識 (2)'!$A$1:$B$296</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2222" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="906">
   <si>
     <t>15-Jähriger</t>
   </si>
@@ -2745,6 +2744,61 @@
   </si>
   <si>
     <t>abweichen</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>克制的保留的謹慎的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>顧及，探討，響應</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>企業</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>zustimmen</t>
+  </si>
+  <si>
+    <t>贊同同意認可</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>obgleich</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hinauszögern</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>猶豫推遲延後</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>gelten</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>被認為被視為適用有效</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>aussehen</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>看起來</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>selbst wenn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>即使</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3118,7 +3172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0134F7F7-897F-8849-B4D3-75368D401457}">
-  <dimension ref="A1:B291"/>
+  <dimension ref="A1:B296"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.1640625" customWidth="1"/>
@@ -3761,226 +3815,226 @@
     </row>
     <row r="81" spans="1:2" ht="18">
       <c r="A81" s="1" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B81" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="18">
       <c r="A82" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B82" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="18">
       <c r="A83" s="1" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B83" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="18">
       <c r="A84" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B84" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="18">
       <c r="A85" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B85" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="18">
       <c r="A86" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B86" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="18">
       <c r="A87" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B87" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="18">
       <c r="A88" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B88" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="18">
       <c r="A89" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B89" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="18">
       <c r="A90" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B90" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="18">
       <c r="A91" s="1" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B91" t="s">
-        <v>351</v>
+        <v>149</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="18">
       <c r="A92" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B92" t="s">
-        <v>149</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="18">
       <c r="A93" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B93" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:2" ht="18">
       <c r="A94" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B94" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="18">
       <c r="A95" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B95" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="18">
       <c r="A96" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B96" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="18">
       <c r="A97" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B97" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="18">
       <c r="A98" s="1" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B98" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="18">
       <c r="A99" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B99" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="18">
       <c r="A100" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B100" t="s">
-        <v>376</v>
+        <v>881</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="18">
       <c r="A101" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B101" t="s">
-        <v>881</v>
+        <v>381</v>
       </c>
     </row>
     <row r="102" spans="1:2" ht="18">
       <c r="A102" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B102" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="18">
       <c r="A103" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B103" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="18">
       <c r="A104" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B104" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="18">
       <c r="A105" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B105" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="106" spans="1:2" ht="18">
       <c r="A106" s="1" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B106" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="107" spans="1:2" ht="18">
       <c r="A107" s="1" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B107" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="18">
       <c r="A108" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B108" t="s">
-        <v>397</v>
+        <v>894</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="18">
@@ -4289,63 +4343,63 @@
     </row>
     <row r="147" spans="1:2" ht="18">
       <c r="A147" s="1" t="s">
-        <v>492</v>
+        <v>902</v>
       </c>
       <c r="B147" t="s">
-        <v>493</v>
+        <v>903</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="18">
       <c r="A148" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B148" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="149" spans="1:2" ht="18">
       <c r="A149" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B149" t="s">
-        <v>37</v>
+        <v>495</v>
       </c>
     </row>
     <row r="150" spans="1:2" ht="18">
       <c r="A150" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B150" t="s">
-        <v>498</v>
+        <v>37</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="18">
       <c r="A151" s="1" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B151" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="18">
       <c r="A152" s="1" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B152" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="153" spans="1:2" ht="18">
       <c r="A153" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B153" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="18">
       <c r="A154" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B154" t="s">
         <v>509</v>
@@ -4353,215 +4407,215 @@
     </row>
     <row r="155" spans="1:2" ht="18">
       <c r="A155" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B155" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="156" spans="1:2" ht="18">
       <c r="A156" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B156" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="18">
       <c r="A157" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B157" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="18">
       <c r="A158" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B158" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="18">
       <c r="A159" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B159" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="18">
       <c r="A160" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B160" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="18">
       <c r="A161" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B161" t="s">
-        <v>868</v>
+        <v>522</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="18">
       <c r="A162" s="1" t="s">
-        <v>869</v>
+        <v>523</v>
       </c>
       <c r="B162" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="18">
       <c r="A163" s="1" t="s">
-        <v>524</v>
+        <v>869</v>
       </c>
       <c r="B163" t="s">
-        <v>525</v>
+        <v>870</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="18">
       <c r="A164" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B164" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="18">
       <c r="A165" s="1" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B165" t="s">
-        <v>37</v>
+        <v>527</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="18">
       <c r="A166" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B166" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="18">
       <c r="A167" s="1" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B167" t="s">
-        <v>536</v>
+        <v>67</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="18">
       <c r="A168" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B168" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="169" spans="1:2" ht="18">
       <c r="A169" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B169" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="18">
       <c r="A170" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B170" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="18">
       <c r="A171" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B171" t="s">
-        <v>544</v>
+        <v>893</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="18">
       <c r="A172" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B172" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="173" spans="1:2" ht="18">
       <c r="A173" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B173" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="18">
       <c r="A174" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B174" t="s">
-        <v>149</v>
+        <v>548</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="18">
       <c r="A175" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B175" t="s">
-        <v>551</v>
+        <v>149</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="18">
       <c r="A176" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B176" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="177" spans="1:2" ht="18">
       <c r="A177" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B177" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="178" spans="1:2" ht="18">
       <c r="A178" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B178" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="179" spans="1:2" ht="18">
       <c r="A179" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B179" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="180" spans="1:2" ht="18">
       <c r="A180" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B180" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="181" spans="1:2" ht="18">
       <c r="A181" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B181" t="s">
         <v>561</v>
@@ -4569,175 +4623,175 @@
     </row>
     <row r="182" spans="1:2" ht="18">
       <c r="A182" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B182" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="183" spans="1:2" ht="18">
       <c r="A183" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B183" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="184" spans="1:2" ht="18">
       <c r="A184" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B184" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="185" spans="1:2" ht="18">
       <c r="A185" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B185" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="186" spans="1:2" ht="18">
       <c r="A186" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B186" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="187" spans="1:2" ht="18">
       <c r="A187" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B187" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="188" spans="1:2" ht="18">
       <c r="A188" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B188" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="189" spans="1:2" ht="18">
       <c r="A189" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B189" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="190" spans="1:2" ht="18">
       <c r="A190" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B190" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="191" spans="1:2" ht="18">
       <c r="A191" s="1" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="B191" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
     </row>
     <row r="192" spans="1:2" ht="18">
       <c r="A192" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B192" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="193" spans="1:2" ht="18">
       <c r="A193" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B193" t="s">
-        <v>872</v>
+        <v>588</v>
       </c>
     </row>
     <row r="194" spans="1:2" ht="18">
       <c r="A194" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B194" t="s">
-        <v>591</v>
+        <v>872</v>
       </c>
     </row>
     <row r="195" spans="1:2" ht="18">
       <c r="A195" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B195" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="196" spans="1:2" ht="18">
       <c r="A196" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B196" t="s">
-        <v>149</v>
+        <v>593</v>
       </c>
     </row>
     <row r="197" spans="1:2" ht="18">
       <c r="A197" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B197" t="s">
-        <v>596</v>
+        <v>149</v>
       </c>
     </row>
     <row r="198" spans="1:2" ht="18">
       <c r="A198" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B198" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="199" spans="1:2" ht="18">
       <c r="A199" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B199" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="200" spans="1:2" ht="18">
       <c r="A200" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B200" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="201" spans="1:2" ht="18">
       <c r="A201" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B201" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="202" spans="1:2" ht="18">
       <c r="A202" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B202" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="203" spans="1:2" ht="18">
       <c r="A203" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B203" t="s">
         <v>606</v>
@@ -4745,705 +4799,745 @@
     </row>
     <row r="204" spans="1:2" ht="18">
       <c r="A204" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B204" t="s">
-        <v>873</v>
+        <v>606</v>
       </c>
     </row>
     <row r="205" spans="1:2" ht="18">
       <c r="A205" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B205" t="s">
-        <v>610</v>
+        <v>873</v>
       </c>
     </row>
     <row r="206" spans="1:2" ht="18">
       <c r="A206" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B206" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="207" spans="1:2" ht="18">
       <c r="A207" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B207" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="208" spans="1:2" ht="18">
       <c r="A208" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B208" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="209" spans="1:2" ht="18">
       <c r="A209" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B209" t="s">
-        <v>155</v>
+        <v>616</v>
       </c>
     </row>
     <row r="210" spans="1:2" ht="18">
       <c r="A210" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B210" t="s">
-        <v>619</v>
+        <v>155</v>
       </c>
     </row>
     <row r="211" spans="1:2" ht="18">
       <c r="A211" s="1" t="s">
-        <v>620</v>
+        <v>900</v>
       </c>
       <c r="B211" t="s">
-        <v>621</v>
+        <v>901</v>
       </c>
     </row>
     <row r="212" spans="1:2" ht="18">
       <c r="A212" s="1" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B212" t="s">
-        <v>623</v>
+        <v>901</v>
       </c>
     </row>
     <row r="213" spans="1:2" ht="18">
       <c r="A213" s="1" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="B213" t="s">
-        <v>886</v>
+        <v>621</v>
       </c>
     </row>
     <row r="214" spans="1:2" ht="18">
       <c r="A214" s="1" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="B214" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
     </row>
     <row r="215" spans="1:2" ht="18">
       <c r="A215" s="1" t="s">
-        <v>632</v>
+        <v>898</v>
       </c>
       <c r="B215" t="s">
-        <v>633</v>
+        <v>899</v>
       </c>
     </row>
     <row r="216" spans="1:2" ht="18">
       <c r="A216" s="1" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="B216" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
     </row>
     <row r="217" spans="1:2" ht="18">
       <c r="A217" s="1" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="B217" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
     </row>
     <row r="218" spans="1:2" ht="18">
       <c r="A218" s="1" t="s">
-        <v>651</v>
+        <v>636</v>
       </c>
       <c r="B218" t="s">
-        <v>652</v>
+        <v>637</v>
       </c>
     </row>
     <row r="219" spans="1:2" ht="18">
       <c r="A219" s="1" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="B219" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
     </row>
     <row r="220" spans="1:2" ht="18">
       <c r="A220" s="1" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="B220" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
     </row>
     <row r="221" spans="1:2" ht="18">
       <c r="A221" s="1" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="B221" t="s">
-        <v>322</v>
+        <v>655</v>
       </c>
     </row>
     <row r="222" spans="1:2" ht="18">
       <c r="A222" s="1" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B222" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="223" spans="1:2" ht="18">
       <c r="A223" s="1" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B223" t="s">
-        <v>662</v>
+        <v>322</v>
       </c>
     </row>
     <row r="224" spans="1:2" ht="18">
       <c r="A224" s="1" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="B224" t="s">
-        <v>509</v>
+        <v>660</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="18">
       <c r="A225" s="1" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B225" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
     </row>
     <row r="226" spans="1:2" ht="18">
       <c r="A226" s="1" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B226" t="s">
-        <v>887</v>
+        <v>509</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="18">
       <c r="A227" s="1" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B227" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
     </row>
     <row r="228" spans="1:2" ht="18">
       <c r="A228" s="1" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B228" t="s">
-        <v>674</v>
+        <v>887</v>
       </c>
     </row>
     <row r="229" spans="1:2" ht="18">
       <c r="A229" s="1" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="B229" t="s">
-        <v>639</v>
+        <v>672</v>
       </c>
     </row>
     <row r="230" spans="1:2" ht="18">
       <c r="A230" s="1" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="B230" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
     </row>
     <row r="231" spans="1:2" ht="18">
       <c r="A231" s="1" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="B231" t="s">
-        <v>685</v>
+        <v>639</v>
       </c>
     </row>
     <row r="232" spans="1:2" ht="18">
       <c r="A232" s="1" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B232" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="233" spans="1:2" ht="18">
       <c r="A233" s="1" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B233" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="234" spans="1:2" ht="18">
       <c r="A234" s="1" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B234" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="235" spans="1:2" ht="18">
       <c r="A235" s="1" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B235" t="s">
-        <v>874</v>
+        <v>689</v>
       </c>
     </row>
     <row r="236" spans="1:2" ht="18">
       <c r="A236" s="1" t="s">
-        <v>697</v>
+        <v>897</v>
       </c>
       <c r="B236" t="s">
-        <v>698</v>
+        <v>317</v>
       </c>
     </row>
     <row r="237" spans="1:2" ht="18">
       <c r="A237" s="1" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="B237" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
     </row>
     <row r="238" spans="1:2" ht="18">
       <c r="A238" s="1" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="B238" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="239" spans="1:2" ht="18">
       <c r="A239" s="1" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="B239" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
     </row>
     <row r="240" spans="1:2" ht="18">
       <c r="A240" s="1" t="s">
-        <v>719</v>
+        <v>701</v>
       </c>
       <c r="B240" t="s">
-        <v>888</v>
+        <v>702</v>
       </c>
     </row>
     <row r="241" spans="1:2" ht="18">
       <c r="A241" s="1" t="s">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="B241" t="s">
-        <v>467</v>
+        <v>875</v>
       </c>
     </row>
     <row r="242" spans="1:2" ht="18">
       <c r="A242" s="1" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="B242" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
     </row>
     <row r="243" spans="1:2" ht="18">
       <c r="A243" s="1" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="B243" t="s">
-        <v>727</v>
+        <v>888</v>
       </c>
     </row>
     <row r="244" spans="1:2" ht="18">
       <c r="A244" s="1" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="B244" t="s">
-        <v>729</v>
+        <v>467</v>
       </c>
     </row>
     <row r="245" spans="1:2" ht="18">
       <c r="A245" s="1" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="B245" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
     </row>
     <row r="246" spans="1:2" ht="18">
       <c r="A246" s="1" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="B246" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
     </row>
     <row r="247" spans="1:2" ht="18">
       <c r="A247" s="1" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="B247" t="s">
-        <v>741</v>
+        <v>729</v>
       </c>
     </row>
     <row r="248" spans="1:2" ht="18">
       <c r="A248" s="1" t="s">
-        <v>742</v>
+        <v>730</v>
       </c>
       <c r="B248" t="s">
-        <v>743</v>
+        <v>731</v>
       </c>
     </row>
     <row r="249" spans="1:2" ht="18">
       <c r="A249" s="1" t="s">
-        <v>750</v>
+        <v>904</v>
       </c>
       <c r="B249" t="s">
-        <v>751</v>
+        <v>905</v>
       </c>
     </row>
     <row r="250" spans="1:2" ht="18">
       <c r="A250" s="1" t="s">
-        <v>756</v>
+        <v>734</v>
       </c>
       <c r="B250" t="s">
-        <v>757</v>
+        <v>735</v>
       </c>
     </row>
     <row r="251" spans="1:2" ht="18">
       <c r="A251" s="1" t="s">
-        <v>759</v>
+        <v>740</v>
       </c>
       <c r="B251" t="s">
-        <v>760</v>
+        <v>741</v>
       </c>
     </row>
     <row r="252" spans="1:2" ht="18">
       <c r="A252" s="1" t="s">
-        <v>761</v>
+        <v>742</v>
       </c>
       <c r="B252" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
     </row>
     <row r="253" spans="1:2" ht="18">
       <c r="A253" s="1" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
       <c r="B253" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
     </row>
     <row r="254" spans="1:2" ht="18">
       <c r="A254" s="1" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B254" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
     </row>
     <row r="255" spans="1:2" ht="18">
       <c r="A255" s="1" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="B255" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
     </row>
     <row r="256" spans="1:2" ht="18">
       <c r="A256" s="1" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="B256" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
     </row>
     <row r="257" spans="1:2" ht="18">
       <c r="A257" s="1" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="B257" t="s">
-        <v>414</v>
+        <v>764</v>
       </c>
     </row>
     <row r="258" spans="1:2" ht="18">
       <c r="A258" s="1" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="B258" t="s">
-        <v>777</v>
+        <v>766</v>
       </c>
     </row>
     <row r="259" spans="1:2" ht="18">
       <c r="A259" s="1" t="s">
-        <v>778</v>
+        <v>767</v>
       </c>
       <c r="B259" t="s">
-        <v>779</v>
+        <v>768</v>
       </c>
     </row>
     <row r="260" spans="1:2" ht="18">
       <c r="A260" s="1" t="s">
-        <v>780</v>
+        <v>769</v>
       </c>
       <c r="B260" t="s">
-        <v>781</v>
+        <v>770</v>
       </c>
     </row>
     <row r="261" spans="1:2" ht="18">
       <c r="A261" s="1" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="B261" t="s">
-        <v>783</v>
+        <v>414</v>
       </c>
     </row>
     <row r="262" spans="1:2" ht="18">
       <c r="A262" s="1" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
       <c r="B262" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
     </row>
     <row r="263" spans="1:2" ht="18">
       <c r="A263" s="1" t="s">
-        <v>789</v>
+        <v>778</v>
       </c>
       <c r="B263" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
     </row>
     <row r="264" spans="1:2" ht="18">
       <c r="A264" s="1" t="s">
-        <v>793</v>
+        <v>780</v>
       </c>
       <c r="B264" t="s">
-        <v>794</v>
+        <v>781</v>
       </c>
     </row>
     <row r="265" spans="1:2" ht="18">
       <c r="A265" s="1" t="s">
-        <v>795</v>
+        <v>782</v>
       </c>
       <c r="B265" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
     </row>
     <row r="266" spans="1:2" ht="18">
       <c r="A266" s="1" t="s">
-        <v>797</v>
+        <v>786</v>
       </c>
       <c r="B266" t="s">
-        <v>798</v>
+        <v>787</v>
       </c>
     </row>
     <row r="267" spans="1:2" ht="18">
       <c r="A267" s="1" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="B267" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
     </row>
     <row r="268" spans="1:2" ht="18">
       <c r="A268" s="1" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="B268" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
     </row>
     <row r="269" spans="1:2" ht="18">
       <c r="A269" s="1" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="B269" t="s">
-        <v>403</v>
+        <v>796</v>
       </c>
     </row>
     <row r="270" spans="1:2" ht="18">
       <c r="A270" s="1" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="B270" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
     </row>
     <row r="271" spans="1:2" ht="18">
       <c r="A271" s="1" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="B271" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
     </row>
     <row r="272" spans="1:2" ht="18">
       <c r="A272" s="1" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="B272" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
     </row>
     <row r="273" spans="1:2" ht="18">
       <c r="A273" s="1" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="B273" t="s">
-        <v>811</v>
+        <v>403</v>
       </c>
     </row>
     <row r="274" spans="1:2" ht="18">
       <c r="A274" s="1" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="B274" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
     </row>
     <row r="275" spans="1:2" ht="18">
       <c r="A275" s="1" t="s">
-        <v>825</v>
+        <v>806</v>
       </c>
       <c r="B275" t="s">
-        <v>548</v>
+        <v>807</v>
       </c>
     </row>
     <row r="276" spans="1:2" ht="18">
       <c r="A276" s="1" t="s">
-        <v>826</v>
+        <v>808</v>
       </c>
       <c r="B276" t="s">
-        <v>827</v>
+        <v>809</v>
       </c>
     </row>
     <row r="277" spans="1:2" ht="18">
       <c r="A277" s="1" t="s">
-        <v>835</v>
+        <v>810</v>
       </c>
       <c r="B277" t="s">
-        <v>836</v>
+        <v>811</v>
       </c>
     </row>
     <row r="278" spans="1:2" ht="18">
       <c r="A278" s="1" t="s">
-        <v>839</v>
+        <v>814</v>
       </c>
       <c r="B278" t="s">
-        <v>197</v>
+        <v>815</v>
       </c>
     </row>
     <row r="279" spans="1:2" ht="18">
       <c r="A279" s="1" t="s">
-        <v>844</v>
+        <v>825</v>
       </c>
       <c r="B279" t="s">
-        <v>845</v>
+        <v>548</v>
       </c>
     </row>
     <row r="280" spans="1:2" ht="18">
       <c r="A280" s="1" t="s">
-        <v>846</v>
+        <v>826</v>
       </c>
       <c r="B280" t="s">
-        <v>847</v>
+        <v>827</v>
       </c>
     </row>
     <row r="281" spans="1:2" ht="18">
       <c r="A281" s="1" t="s">
-        <v>848</v>
+        <v>835</v>
       </c>
       <c r="B281" t="s">
-        <v>849</v>
+        <v>836</v>
       </c>
     </row>
     <row r="282" spans="1:2" ht="18">
       <c r="A282" s="1" t="s">
-        <v>850</v>
+        <v>839</v>
       </c>
       <c r="B282" t="s">
-        <v>851</v>
+        <v>197</v>
       </c>
     </row>
     <row r="283" spans="1:2" ht="18">
       <c r="A283" s="1" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="B283" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="284" spans="1:2" ht="18">
       <c r="A284" s="1" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="B284" t="s">
-        <v>796</v>
+        <v>847</v>
       </c>
     </row>
     <row r="285" spans="1:2" ht="18">
       <c r="A285" s="1" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="B285" t="s">
-        <v>729</v>
+        <v>849</v>
       </c>
     </row>
     <row r="286" spans="1:2" ht="18">
       <c r="A286" s="1" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="B286" t="s">
-        <v>857</v>
+        <v>892</v>
       </c>
     </row>
     <row r="287" spans="1:2" ht="18">
       <c r="A287" s="1" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="B287" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="288" spans="1:2" ht="18">
       <c r="A288" s="1" t="s">
-        <v>860</v>
+        <v>895</v>
       </c>
       <c r="B288" t="s">
-        <v>582</v>
+        <v>896</v>
       </c>
     </row>
     <row r="289" spans="1:2" ht="18">
       <c r="A289" s="1" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="B289" t="s">
-        <v>473</v>
+        <v>796</v>
       </c>
     </row>
     <row r="290" spans="1:2" ht="18">
       <c r="A290" s="1" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="B290" t="s">
-        <v>863</v>
+        <v>729</v>
       </c>
     </row>
     <row r="291" spans="1:2" ht="18">
       <c r="A291" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="B291" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" ht="18">
+      <c r="A292" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="B292" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" ht="18">
+      <c r="A293" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="B293" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" ht="18">
+      <c r="A294" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="B294" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" ht="18">
+      <c r="A295" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="B295" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" ht="18">
+      <c r="A296" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="B291" t="s">
+      <c r="B296" t="s">
         <v>865</v>
       </c>
     </row>
